--- a/data/trans_bre/IP19C09-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP19C09-Edad-trans_bre.xlsx
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,54; -0,25</t>
+          <t>-9,5; -0,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 5,46</t>
+          <t>-4,14; 4,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 5,46</t>
+          <t>-7,1; 5,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 21,65</t>
+          <t>-100,0; 121,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 651,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 268,31</t>
+          <t>-91,04; 439,63</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 4,37</t>
+          <t>-0,88; 4,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 0,6</t>
+          <t>-4,54; 0,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 5,12</t>
+          <t>-0,16; 5,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-64,57; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -874,22 +874,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 0,2</t>
+          <t>-4,93; 0,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 2,93</t>
+          <t>-1,49; 2,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 1,15</t>
+          <t>-3,98; 1,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 74,72</t>
+          <t>-91,79; 53,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 253,35</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 0,02</t>
+          <t>-3,46; 0,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 1,45</t>
+          <t>-1,89; 1,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 2,12</t>
+          <t>-1,87; 2,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-83,86; 9,42</t>
+          <t>-82,53; 23,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-69,87; 181,96</t>
+          <t>-71,67; 146,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-58,11; 132,93</t>
+          <t>-55,8; 140,39</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C09-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP19C09-Edad-trans_bre.xlsx
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,5; -0,07</t>
+          <t>-9,38; -0,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 4,97</t>
+          <t>-4,42; 5,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 5,8</t>
+          <t>-7,39; 4,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 121,33</t>
+          <t>-100,0; 47,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 651,44</t>
+          <t>-100,0; 662,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-91,04; 439,63</t>
+          <t>-100,0; 284,46</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 4,62</t>
+          <t>-0,62; 4,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 0,54</t>
+          <t>-4,33; 0,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 5,3</t>
+          <t>-0,38; 5,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-49,25; —</t>
         </is>
       </c>
     </row>
@@ -874,22 +874,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 0,28</t>
+          <t>-4,69; 0,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 2,95</t>
+          <t>-1,53; 2,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 1,21</t>
+          <t>-4,01; 1,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-91,79; 53,02</t>
+          <t>-100,0; 47,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 253,35</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 0,11</t>
+          <t>-3,56; 0,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 1,44</t>
+          <t>-1,91; 1,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 2,01</t>
+          <t>-1,69; 2,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-82,53; 23,01</t>
+          <t>-85,52; 16,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-71,67; 146,77</t>
+          <t>-70,99; 159,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-55,8; 140,39</t>
+          <t>-54,12; 165,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C09-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP19C09-Edad-trans_bre.xlsx
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,38; -0,01</t>
+          <t>-8,54; -0,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 5,2</t>
+          <t>-4,26; 5,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 4,79</t>
+          <t>-7,45; 5,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 47,12</t>
+          <t>-100,0; 21,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 662,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 284,46</t>
+          <t>-100,0; 268,31</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 4,69</t>
+          <t>-0,62; 4,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 0,59</t>
+          <t>-4,38; 0,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 5,15</t>
+          <t>-0,13; 5,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-49,25; —</t>
+          <t>-64,57; —</t>
         </is>
       </c>
     </row>
@@ -874,22 +874,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 0,51</t>
+          <t>-5,31; 0,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 2,97</t>
+          <t>-1,56; 2,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 1,39</t>
+          <t>-4,18; 1,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 47,91</t>
+          <t>-100,0; 74,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 0,19</t>
+          <t>-3,62; 0,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 1,53</t>
+          <t>-1,81; 1,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 2,15</t>
+          <t>-1,86; 2,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-85,52; 16,02</t>
+          <t>-83,86; 9,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-70,99; 159,07</t>
+          <t>-69,87; 181,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-54,12; 165,96</t>
+          <t>-58,11; 132,93</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C09-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP19C09-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,133 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>18,84</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>18.84288197991866</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr"/>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-4,08</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,17</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-1,18</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-73,33%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-5,35%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-21,7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-8,54; -0,25</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-4,26; 5,46</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-7,45; 5,46</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 21,65</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 268,31</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-4.077290496173561</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.1703155248673954</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-1.179025364247861</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.7333238094344706</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.05347614243946364</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.2169827805054227</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,94</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-1,25</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,26</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>153,74%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-69,97%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>237,33%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-8.539576626996595</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-4.262439866348074</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-7.452530440384407</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-0,62; 4,37</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-4,38; 0,6</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-0,13; 5,12</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-64,57; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>-0.2511705388935753</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>5.464408949216057</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>5.46086277522923</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.2164838911579512</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="n">
+        <v>2.683145094812731</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,157 +737,225 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-2,15</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,46</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-1,14</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-62,67%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>47,05%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-51,46%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.9438786646951941</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-1.252814495978761</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>2.255019740481222</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>1.537373583032645</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.6996759014883155</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>2.373267421247991</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-5,31; 0,2</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-1,56; 2,93</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-4,18; 1,15</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 74,72</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-0.6183523892673972</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-4.376586589796693</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-0.1261401948495521</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="n">
+        <v>-0.6456883635061618</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>4.374676753204731</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.6007025800991608</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>5.120096924464185</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-2.153776495562797</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.4633532361831472</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-1.135121216416459</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.6267386663508442</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.4704565311602157</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.5146167506016186</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-5.314146916908789</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-1.562422778604215</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-4.181312667989415</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.1998733082920223</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.93165453133051</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.152593531842373</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.7471682689908149</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-1,67</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,19</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,13</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-54,52%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-10,63%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,31%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-3,62; 0,02</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-1,81; 1,45</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-1,86; 2,12</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-83,86; 9,42</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-69,87; 181,96</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-58,11; 132,93</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-1.671419679464448</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.1938696565544074</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.1283082115822249</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>-0.545203008732238</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.1062768404491198</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.05305336910917367</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-3.617815544654816</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.808478617752896</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.858607911069198</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-0.8385625379426065</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.6986507045858715</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.5810627472797583</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.01866911455452469</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.446720939344781</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2.122949803087668</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>0.09421649981187356</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>1.819562085037443</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1.32929966705838</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -993,13 +964,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
